--- a/reports/telegram/aegis_daily_2026-08-20.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV17"/>
+  <dimension ref="A1:AV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R2-BMY-USA-20260811-8b789e</t>
+          <t>R2-PLTR-USA-20260810-caa9a7</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BMY_USA_20260811</t>
+          <t>PLTR_USA_20260810</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -758,24 +758,24 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>77.3</v>
+        <v>76</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>59.8</v>
+        <v>57.4</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>-0.8</v>
@@ -795,12 +795,12 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 60% · band HOLD · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 58% · band HOLD · 17d left · → BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>60.5</v>
+        <v>58.2</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>33.6</v>
+        <v>32.9</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z2" s="3" t="n">
         <v>17</v>
@@ -824,44 +824,44 @@
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>67.61</v>
+        <v>175.08</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>67.61</v>
+        <v>175.08</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>66.93000000000001</v>
+        <v>173.33</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>68.29000000000001</v>
+        <v>176.83</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>63.55</v>
+        <v>164.58</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>-6.01</v>
+        <v>-6</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>75.72</v>
+        <v>196.09</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>83.84</v>
+        <v>217.1</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>24.01</v>
+        <v>24</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>66.05</v>
+        <v>175.19</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>2.36</v>
+        <v>-0.06</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>0</v>
@@ -874,31 +874,31 @@
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Trend · Growth · Event Driven</t>
+          <t>Value · Quality · Growth</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr"/>
       <c r="AT2" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R2-PLTR-USA-20260810-caa9a7</t>
+          <t>R2-BMY-USA-20260811-8b789e</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PLTR_USA_20260810</t>
+          <t>BMY_USA_20260811</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -918,24 +918,24 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>75.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>53.7</v>
+        <v>63.8</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>-0.8</v>
@@ -955,12 +955,12 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 54% · band HOLD · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 65% · band HOLD · 17d left · → HOLD</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>54.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>33.1</v>
+        <v>32.8</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z3" s="3" t="n">
         <v>17</v>
@@ -984,44 +984,44 @@
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>175.19</v>
+        <v>66.87</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>175.19</v>
+        <v>66.87</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>173.44</v>
+        <v>66.2</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>176.94</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>164.68</v>
+        <v>63.53</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>-6</v>
+        <v>-4.99</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>196.21</v>
+        <v>72.22</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>217.24</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>171.54</v>
+        <v>67.61</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>2.13</v>
+        <v>-1.09</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>0</v>
@@ -1034,19 +1034,17 @@
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Value · Quality · Growth</t>
+          <t>Growth · Trend · Event Driven</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
@@ -1084,18 +1082,18 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="n">
-        <v>81.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -1103,7 +1101,7 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>52.5</v>
+        <v>56.4</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>-0.8</v>
@@ -1115,12 +1113,12 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 53% · band STRONG · 9d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 57% · band HOLD · 17d left · → HOLD</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>53.2</v>
+        <v>57.2</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1128,7 +1126,7 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>1</v>
@@ -1137,10 +1135,10 @@
         <v>8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
@@ -1148,40 +1146,40 @@
         </is>
       </c>
       <c r="AC4" s="3" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>189.98</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>193.82</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>182.31</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>207.25</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>220.69</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM4" s="3" t="n">
         <v>192.82</v>
       </c>
-      <c r="AD4" s="3" t="n">
-        <v>192.82</v>
-      </c>
-      <c r="AE4" s="3" t="n">
-        <v>190.89</v>
-      </c>
-      <c r="AF4" s="3" t="n">
-        <v>194.75</v>
-      </c>
-      <c r="AG4" s="3" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="AH4" s="3" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AI4" s="3" t="n">
-        <v>215.96</v>
-      </c>
-      <c r="AJ4" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK4" s="3" t="n">
-        <v>239.1</v>
-      </c>
-      <c r="AL4" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM4" s="3" t="n">
-        <v>182.07</v>
-      </c>
       <c r="AN4" s="3" t="n">
-        <v>5.9</v>
+        <v>-0.48</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>0</v>
@@ -1198,27 +1196,25 @@
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R2-SNA-USA-20260811-3cf333</t>
+          <t>R2-DXCM-USA-20260811-6fdebc</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SNA_USA_20260811</t>
+          <t>DXCM_USA_20260811</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1238,38 +1234,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>→ BMY · +59.4pp alpha</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>52.9</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>34.3</v>
+        <v>60.7</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>-0.8</v>
@@ -1281,12 +1271,12 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #11 · Conf 35% · band EXIT · 60d left · → EXIT (rotate to BMY)</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #7 · Conf 61% · band STRONG · 60d left · → HOLD</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>35</v>
+        <v>61.4</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1294,7 +1284,7 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-25.8</v>
+        <v>29.7</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>1</v>
@@ -1314,40 +1304,40 @@
         </is>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>393.93</v>
+        <v>90.78</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>393.93</v>
+        <v>90.78</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>389.99</v>
+        <v>89.87</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>397.87</v>
+        <v>91.69</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>374.23</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="AH5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>425.44</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="AJ5" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>453.02</v>
+        <v>104.4</v>
       </c>
       <c r="AL5" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>393.27</v>
+        <v>89.88</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>0</v>
@@ -1360,29 +1350,29 @@
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+          <t>Trend · Momentum · News</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr"/>
       <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>59.35</v>
+        <v>0</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-EIX-USA-20260814-736f75</t>
+          <t>R2-PKG-USA-20260811-313356</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EIX_USA_20260814</t>
+          <t>PKG_USA_20260811</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1397,37 +1387,43 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>→ UBER · +60.5pp alpha</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="n">
-        <v>64.8</v>
+        <v>52.9</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>59.8</v>
+        <v>34.8</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>-0.8</v>
@@ -1439,12 +1435,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 60% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #11 · Conf 36% · band EXIT · 60d left · → EXIT (rotate to UBER)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>60.5</v>
+        <v>35.5</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1452,58 +1448,60 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="X6" s="3" t="inlineStr"/>
+        <v>-26.3</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>73.44</v>
+        <v>251.68</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>73.44</v>
+        <v>251.68</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>71.97</v>
+        <v>249.16</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>74.91</v>
+        <v>254.2</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>69.768</v>
+        <v>239.1</v>
       </c>
       <c r="AH6" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>79.3152</v>
+        <v>271.81</v>
       </c>
       <c r="AJ6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>84.86726400000001</v>
+        <v>289.43</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>73.69</v>
+        <v>252.91</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.49</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>0</v>
@@ -1514,33 +1512,31 @@
       <c r="AQ6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
       <c r="AU6" s="3" t="n">
-        <v>8</v>
+        <v>60.5</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-PLTR-USA-20260810-9c1c66</t>
+          <t>R2-CL-USA-20260811-e50dd0</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>PLTR_USA_20260810</t>
+          <t>CL_USA_20260811</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1555,37 +1551,43 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>→ UBER · +60.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="n">
-        <v>75.8</v>
+        <v>53</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>53.7</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>-0.8</v>
@@ -1597,12 +1599,12 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #12 · Conf 37% · band EXIT · 60d left · → EXIT (rotate to UBER)</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>54.4</v>
+        <v>37.4</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1610,58 +1612,60 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="X7" s="3" t="inlineStr"/>
+        <v>-26.5</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y7" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>175.19</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>175.19</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>173.44</v>
+        <v>89.56</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>176.94</v>
+        <v>91.36</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>166.4305</v>
+        <v>85.94</v>
       </c>
       <c r="AH7" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>196.21</v>
+        <v>97.7</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>209.9447</v>
+        <v>104.03</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>19.84</v>
+        <v>15</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>171.54</v>
+        <v>90.87</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>2.13</v>
+        <v>-0.45</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>0</v>
@@ -1672,33 +1676,31 @@
       <c r="AQ7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="n">
-        <v>12</v>
+        <v>60.63</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-BMY-USA-20260814-d14184</t>
+          <t>R1-GOOGL-USA-20260819-063f97</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BMY_USA_20260814</t>
+          <t>GOOGL_USA_20260819</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1718,10 +1720,14 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>BMY</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1730,12 +1736,12 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="n">
-        <v>77.3</v>
+        <v>70.5</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -1743,24 +1749,24 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>59.8</v>
+        <v>60.4</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 51 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 60% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 61% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>60.5</v>
+        <v>61.2</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1768,11 +1774,11 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>90</v>
@@ -1782,44 +1788,44 @@
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>67.61</v>
+        <v>342.06</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>67.61</v>
+        <v>342.06</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>66.93000000000001</v>
+        <v>338.64</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>68.29000000000001</v>
+        <v>345.49</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>64.2295</v>
+        <v>324.957</v>
       </c>
       <c r="AH8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>75.72</v>
+        <v>383.11</v>
       </c>
       <c r="AJ8" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>81.02040000000001</v>
+        <v>409.9277</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>19.83</v>
+        <v>19.84</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>66.05</v>
+        <v>344.72</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>2.36</v>
+        <v>-0.77</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>0</v>
@@ -1844,19 +1850,19 @@
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-GOOGL-USA-20260819-063f97</t>
+          <t>R1-UBER-USA-20260810-2e9fcb</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>GOOGL_USA_20260819</t>
+          <t>UBER_USA_20260810</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1876,14 +1882,10 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Alphabet</t>
-        </is>
-      </c>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1892,12 +1894,12 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -1905,24 +1907,24 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>56.6</v>
+        <v>60.7</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 51 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 61% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>57.3</v>
+        <v>61.4</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1930,11 +1932,11 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>90</v>
@@ -1944,44 +1946,44 @@
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>344.72</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>344.72</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>337.83</v>
+        <v>77.97</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>351.61</v>
+        <v>79.55</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>327.484</v>
+        <v>74.822</v>
       </c>
       <c r="AH9" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>372.2976</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>398.3584320000001</v>
+        <v>94.3847</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>344.2</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.15</v>
+        <v>0.92</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>0</v>
@@ -2002,23 +2004,23 @@
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-UBER-USA-20260810-2e9fcb</t>
+          <t>R1-EIX-USA-20260814-736f75</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UBER_USA_20260810</t>
+          <t>EIX_USA_20260814</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2038,7 +2040,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -2050,12 +2052,12 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2065,7 @@
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>56.7</v>
+        <v>63.8</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>-0.8</v>
@@ -2075,12 +2077,12 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 65% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>57.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2088,11 +2090,11 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>65</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>90</v>
@@ -2102,44 +2104,44 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>78.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>78.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>76.48</v>
+        <v>73.11</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>76.09</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>74.13800000000001</v>
+        <v>70.86999999999999</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>84.28320000000001</v>
+        <v>80.568</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>90.18302400000002</v>
+        <v>86.20776000000001</v>
       </c>
       <c r="AL10" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>74.66</v>
+        <v>73.44</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>4.53</v>
+        <v>1.58</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>0</v>
@@ -2164,19 +2166,19 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-IT-USA-20260810-b67168</t>
+          <t>R1-DXCM-USA-20260820-69dcad</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>IT_USA_20260810</t>
+          <t>DXCM_USA_20260820</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2196,7 +2198,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -2208,12 +2210,12 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>81.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2223,7 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>52.5</v>
+        <v>60.7</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-0.8</v>
@@ -2233,12 +2235,12 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 53% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 61% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>53.2</v>
+        <v>61.4</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2246,11 +2248,11 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>58.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>90</v>
@@ -2260,44 +2262,44 @@
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>192.82</v>
+        <v>90.78</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>192.82</v>
+        <v>90.78</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>190.89</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>194.75</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>183.179</v>
+        <v>86.241</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>215.96</v>
+        <v>98.0424</v>
       </c>
       <c r="AJ11" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>231.0772</v>
+        <v>104.905368</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>19.84</v>
+        <v>15.56</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>182.07</v>
+        <v>89.88</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>0</v>
@@ -2318,23 +2320,23 @@
         <v>5</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R1-ADBE-USA-20260810-009819</t>
+          <t>R1-PLTR-USA-20260810-9c1c66</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ADBE_USA_20260810</t>
+          <t>PLTR_USA_20260810</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2354,14 +2356,10 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ADBE</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -2370,12 +2368,12 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="n">
-        <v>82.2</v>
+        <v>76</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2383,7 +2381,7 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>59.7</v>
+        <v>57.4</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>-0.8</v>
@@ -2395,12 +2393,12 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 60% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 58% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>60.4</v>
+        <v>58.2</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2408,7 +2406,7 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>54</v>
+        <v>70.7</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
@@ -2426,40 +2424,40 @@
         </is>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>272.47</v>
+        <v>175.08</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>272.47</v>
+        <v>175.08</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>267.02</v>
+        <v>173.33</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>277.92</v>
+        <v>176.83</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>258.8465</v>
+        <v>166.326</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>294.2676000000001</v>
+        <v>196.09</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>314.8663320000001</v>
+        <v>209.8163</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>263.14</v>
+        <v>175.19</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>3.55</v>
+        <v>-0.06</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
@@ -2480,23 +2478,23 @@
         <v>5</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R1-SAIC-USA-20260814-c21f0d</t>
+          <t>R1-BMY-USA-20260814-d14184</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SAIC_USA_20260814</t>
+          <t>BMY_USA_20260814</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2516,7 +2514,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -2528,12 +2526,12 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="n">
-        <v>71.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2541,7 +2539,7 @@
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>56.7</v>
+        <v>63.8</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>-0.8</v>
@@ -2553,12 +2551,12 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 65% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>57.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2564,7 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>53.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
@@ -2584,40 +2582,40 @@
         </is>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>128.71</v>
+        <v>66.87</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>128.71</v>
+        <v>66.87</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>126.14</v>
+        <v>65.53</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>131.28</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>122.2745</v>
+        <v>63.5265</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>139.0068</v>
+        <v>72.21960000000001</v>
       </c>
       <c r="AJ13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>148.737276</v>
+        <v>77.27497200000002</v>
       </c>
       <c r="AL13" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>125.95</v>
+        <v>67.61</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>2.19</v>
+        <v>-1.09</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
@@ -2642,19 +2640,19 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R1-MSFT-USA-20260810-673c2d</t>
+          <t>R1-IT-USA-20260810-b67168</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MSFT_USA_20260810</t>
+          <t>IT_USA_20260810</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2674,28 +2672,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="n">
-        <v>81.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2703,24 +2697,24 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>53.4</v>
+        <v>56.4</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 54% · momentum → · band HOLD→STRONG · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>54.2</v>
+        <v>57.2</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2728,7 +2722,7 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>47.3</v>
+        <v>59.4</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
@@ -2746,40 +2740,40 @@
         </is>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>484.31</v>
+        <v>191.9</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>484.31</v>
+        <v>191.9</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>474.62</v>
+        <v>188.06</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>494</v>
+        <v>195.74</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>460.0945</v>
+        <v>182.305</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>523.0548</v>
+        <v>207.252</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>559.668636</v>
+        <v>221.75964</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>481.63</v>
+        <v>192.82</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
@@ -2804,19 +2798,19 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R1-CRM-USA-20260814-a67586</t>
+          <t>R1-MSFT-USA-20260810-673c2d</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CRM_USA_20260814</t>
+          <t>MSFT_USA_20260810</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2836,12 +2830,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2852,12 +2846,12 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2865,24 +2859,24 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>55.1</v>
+        <v>57</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 56% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 58% · momentum → · band HOLD→STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>55.9</v>
+        <v>57.8</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2890,11 +2884,11 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>36.6</v>
+        <v>48.4</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>90</v>
@@ -2904,44 +2898,44 @@
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>206.09</v>
+        <v>482.05</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>206.09</v>
+        <v>482.05</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>201.97</v>
+        <v>472.41</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>210.21</v>
+        <v>491.69</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>195.7855</v>
+        <v>457.9475</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>222.5772</v>
+        <v>520.614</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>238.157604</v>
+        <v>557.0569800000001</v>
       </c>
       <c r="AL15" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>196.14</v>
+        <v>484.31</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>5.07</v>
+        <v>-0.47</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>0</v>
@@ -2966,19 +2960,19 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-TRV-USA-20260810-a2c57b</t>
+          <t>R1-CRM-USA-20260814-a67586</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TRV_USA_20260810</t>
+          <t>CRM_USA_20260814</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2993,17 +2987,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -3014,27 +3008,37 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 65% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>56.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -3042,61 +3046,95 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>29.2</v>
+        <v>46.4</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="n">
+        <v>205.34</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>205.34</v>
+      </c>
+      <c r="AE16" s="3" t="n">
+        <v>201.23</v>
+      </c>
+      <c r="AF16" s="3" t="n">
+        <v>209.45</v>
+      </c>
+      <c r="AG16" s="3" t="n">
+        <v>195.073</v>
+      </c>
+      <c r="AH16" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>221.7672</v>
+      </c>
+      <c r="AJ16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Z16" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA16" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AC16" s="3" t="inlineStr"/>
-      <c r="AD16" s="3" t="inlineStr"/>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="n">
+        <v>237.290904</v>
+      </c>
+      <c r="AL16" s="3" t="n">
+        <v>15.56</v>
+      </c>
       <c r="AM16" s="3" t="n">
-        <v>367.93</v>
+        <v>206.09</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
+        <v>-0.36</v>
+      </c>
+      <c r="AO16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20 08:43</t>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-V-USA-20260810-1697f4</t>
+          <t>R1-SAIC-USA-20260814-c21f0d</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>V_USA_20260810</t>
+          <t>SAIC_USA_20260814</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3111,19 +3149,15 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3132,27 +3166,37 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 58% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>53.6</v>
+        <v>58.2</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -3160,54 +3204,324 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>27.8</v>
+        <v>33.5</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="n">
+        <v>128.59</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>128.59</v>
+      </c>
+      <c r="AE17" s="3" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="AF17" s="3" t="n">
+        <v>131.16</v>
+      </c>
+      <c r="AG17" s="3" t="n">
+        <v>122.1605</v>
+      </c>
+      <c r="AH17" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>138.8772</v>
+      </c>
+      <c r="AJ17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Z17" s="3" t="n">
+      <c r="AK17" s="3" t="n">
+        <v>148.598604</v>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM17" s="3" t="n">
+        <v>128.71</v>
+      </c>
+      <c r="AN17" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AO17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="3" t="inlineStr"/>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260810</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="AA17" s="3" t="n">
+      <c r="AA18" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB17" s="3" t="inlineStr">
+      <c r="AB18" s="3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="AC17" s="3" t="inlineStr"/>
-      <c r="AD17" s="3" t="inlineStr"/>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="n">
-        <v>364.25</v>
-      </c>
-      <c r="AN17" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20 08:43</t>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
+      <c r="AM18" s="3" t="n">
+        <v>362.22</v>
+      </c>
+      <c r="AN18" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr"/>
+      <c r="AS18" s="3" t="inlineStr"/>
+      <c r="AT18" s="3" t="inlineStr"/>
+      <c r="AU18" s="3" t="inlineStr"/>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>R2-V-USA-20260810-1697f4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>V_USA_20260810</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA19" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="AN19" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr"/>
+      <c r="AS19" s="3" t="inlineStr"/>
+      <c r="AT19" s="3" t="inlineStr"/>
+      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV17"/>
+  <autoFilter ref="A1:AV19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>